--- a/Kolkata_Car_Bike_Route_Coordinates_and_Links.xlsx
+++ b/Kolkata_Car_Bike_Route_Coordinates_and_Links.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>22.527158250575937, 88.32629182603299</t>
+          <t>22.526862452154507, 88.32590541146433</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
